--- a/Data/Excel_Thi/data/6.xlsx
+++ b/Data/Excel_Thi/data/6.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\MOS360\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell7390\Desktop\File đề test\TEST EXCEL_11P\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09849054-DB24-4E0C-B0F2-74821DA2C4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54348F00-6134-4368-9A1E-E574C1910D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-30" windowWidth="28920" windowHeight="12960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enrollment Summary" sheetId="1" r:id="rId1"/>
@@ -165,14 +165,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -180,7 +180,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -188,7 +188,7 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -269,7 +269,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -284,12 +284,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="32" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     </dxf>
@@ -2242,15 +2246,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A3:F21" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A3:F21" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A3:F21" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Program"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Category"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Students Enrollment"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tutors Available "/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Average Cost" dataDxfId="3" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Total" dataDxfId="2" dataCellStyle="Currency">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Average Cost" dataDxfId="4" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Total" dataDxfId="3" dataCellStyle="Currency">
       <calculatedColumnFormula>E4*C4</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2266,8 +2270,8 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Category"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Students Enrolled"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tutors Available"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Average Cost per Student" dataDxfId="1" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Total" dataDxfId="0">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Average Cost per Student" dataDxfId="2" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Total" dataDxfId="1">
       <calculatedColumnFormula>SUM(E4*C4)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2539,23 +2543,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.875" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2563,7 +2567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -2571,7 +2575,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
@@ -2579,7 +2583,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -2587,7 +2591,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>13</v>
       </c>
@@ -2604,47 +2608,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5" customWidth="1"/>
-    <col min="4" max="4" width="17.25" customWidth="1"/>
-    <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -2665,7 +2669,7 @@
         <v>68400</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -2686,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2707,7 +2711,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -2728,7 +2732,7 @@
         <v>56250</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -2749,7 +2753,7 @@
         <v>104000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -2770,7 +2774,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -2791,7 +2795,7 @@
         <v>12900</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2812,7 +2816,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -2833,7 +2837,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -2854,7 +2858,7 @@
         <v>82500</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -2875,7 +2879,7 @@
         <v>25600</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -2896,7 +2900,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -2917,7 +2921,7 @@
         <v>45500</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -2938,7 +2942,7 @@
         <v>31500</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2959,7 +2963,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -2980,7 +2984,7 @@
         <v>77400</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -3001,7 +3005,7 @@
         <v>21250</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -3034,27 +3038,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" customWidth="1"/>
-    <col min="4" max="4" width="16.75" customWidth="1"/>
-    <col min="5" max="5" width="25.25" customWidth="1"/>
-    <col min="6" max="6" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" customWidth="1"/>
+    <col min="5" max="5" width="25.21875" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3074,7 +3078,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -3095,7 +3099,7 @@
         <v>57000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -3116,7 +3120,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3137,7 +3141,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -3158,7 +3162,7 @@
         <v>41250</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -3179,7 +3183,7 @@
         <v>104000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -3200,7 +3204,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -3221,7 +3225,7 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -3242,7 +3246,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -3263,7 +3267,7 @@
         <v>22500</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -3284,7 +3288,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -3305,7 +3309,7 @@
         <v>25600</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -3326,7 +3330,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -3347,7 +3351,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -3368,7 +3372,7 @@
         <v>24500</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3389,7 +3393,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -3410,7 +3414,7 @@
         <v>58050</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -3431,7 +3435,7 @@
         <v>51000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -3464,22 +3468,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3487,7 +3491,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3495,7 +3499,7 @@
         <v>282400</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -3503,7 +3507,7 @@
         <v>103100</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3511,7 +3515,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
